--- a/schema/tots/_defs.xlsx
+++ b/schema/tots/_defs.xlsx
@@ -547,7 +547,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -694,9 +694,38 @@
         <v>Explicit ordinary data row</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>standard</v>
+      </c>
+      <c r="B6" t="str">
+        <v>MODUSTESTID</v>
+      </c>
+      <c r="C6" t="str">
+        <v>modusTestIds</v>
+      </c>
+      <c r="D6" t="str">
+        <v>one</v>
+      </c>
+      <c r="E6" t="str">
+        <v>by-column</v>
+      </c>
+      <c r="F6" t="str">
+        <v>table</v>
+      </c>
+      <c r="G6" t="str">
+        <v>captures per-column Modus test id strings</v>
+      </c>
+      <c r="H6" t="str">
+        <v>false</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Per-column Modus test identifier row</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I6"/>
   </ignoredErrors>
 </worksheet>
 </file>